--- a/public/ŞEBEKE-KANAL-TR.xlsx
+++ b/public/ŞEBEKE-KANAL-TR.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\New folder\setash\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\back-setash\setash\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D92B1B-924B-4C01-A97B-1FC07C2251CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3558A7E-82F6-4DD4-8385-FD57B5E6A948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{495C7B08-8481-4DB8-BE2C-ACDD32DDBC17}"/>
   </bookViews>
